--- a/reports/api-test-2026-06-29/full-api-report.xlsx
+++ b/reports/api-test-2026-06-29/full-api-report.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6109536-0C4D-46B8-B48A-D317CDC5EEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="AllAPIs" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="SlowAPIs_gt200ms" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Summary" state="visible" r:id="rId6"/>
+    <sheet name="AllAPIs" sheetId="1" r:id="rId1"/>
+    <sheet name="SlowAPIs_gt200ms" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -220,9 +224,6 @@
   </si>
   <si>
     <t>{"success":false,"message":"Listener profile not found"}</t>
-  </si>
-  <si>
-    <t>404 if customer has no listener profile</t>
   </si>
   <si>
     <t>Expected 200|201|204, got 404</t>
@@ -1182,18 +1183,21 @@
   <si>
     <t>Use insertMany/bulk; defer wallet seed to background job</t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1556,9 +1560,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I164"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1566,7 +1570,7 @@
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="80" customWidth="1"/>
+    <col min="8" max="8" width="148.28515625" customWidth="1"/>
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2292,7 +2296,7 @@
         <v>68</v>
       </c>
       <c r="I25" t="s">
-        <v>69</v>
+        <v>385</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2321,7 +2325,7 @@
         <v>68</v>
       </c>
       <c r="I26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -2332,7 +2336,7 @@
         <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
         <v>43</v>
@@ -2347,7 +2351,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
@@ -2361,7 +2365,7 @@
         <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
         <v>43</v>
@@ -2376,7 +2380,7 @@
         <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
@@ -2390,7 +2394,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
         <v>43</v>
@@ -2405,7 +2409,7 @@
         <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
@@ -2419,7 +2423,7 @@
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>43</v>
@@ -2434,7 +2438,7 @@
         <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
@@ -2448,7 +2452,7 @@
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>43</v>
@@ -2463,7 +2467,7 @@
         <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
@@ -2477,7 +2481,7 @@
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
         <v>43</v>
@@ -2492,7 +2496,7 @@
         <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
@@ -2506,10 +2510,10 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
         <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
       </c>
       <c r="E33">
         <v>200</v>
@@ -2521,7 +2525,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
@@ -2535,10 +2539,10 @@
         <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34">
         <v>200</v>
@@ -2550,7 +2554,7 @@
         <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
@@ -2564,10 +2568,10 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35">
         <v>201</v>
@@ -2579,7 +2583,7 @@
         <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
@@ -2587,13 +2591,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
         <v>90</v>
-      </c>
-      <c r="B36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" t="s">
-        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>22</v>
@@ -2608,7 +2612,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
@@ -2616,13 +2620,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B37" t="s">
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" t="s">
         <v>22</v>
@@ -2637,7 +2641,7 @@
         <v>13</v>
       </c>
       <c r="H37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
@@ -2645,13 +2649,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
         <v>36</v>
@@ -2666,7 +2670,7 @@
         <v>13</v>
       </c>
       <c r="H38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
@@ -2674,13 +2678,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
         <v>96</v>
-      </c>
-      <c r="B39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" t="s">
-        <v>97</v>
       </c>
       <c r="D39" t="s">
         <v>22</v>
@@ -2695,7 +2699,7 @@
         <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
@@ -2703,13 +2707,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
         <v>22</v>
@@ -2724,7 +2728,7 @@
         <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
@@ -2732,13 +2736,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D41" t="s">
         <v>36</v>
@@ -2753,7 +2757,7 @@
         <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
@@ -2761,13 +2765,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
@@ -2782,21 +2786,21 @@
         <v>13</v>
       </c>
       <c r="H42" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" t="s">
         <v>104</v>
-      </c>
-      <c r="I42" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
         <v>22</v>
@@ -2811,7 +2815,7 @@
         <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
@@ -2819,13 +2823,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
         <v>43</v>
@@ -2840,7 +2844,7 @@
         <v>13</v>
       </c>
       <c r="H44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
@@ -2848,13 +2852,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -2869,7 +2873,7 @@
         <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
@@ -2877,13 +2881,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
         <v>22</v>
@@ -2898,7 +2902,7 @@
         <v>13</v>
       </c>
       <c r="H46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
@@ -2906,13 +2910,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
         <v>22</v>
@@ -2927,21 +2931,21 @@
         <v>13</v>
       </c>
       <c r="H47" t="s">
+        <v>113</v>
+      </c>
+      <c r="I47" t="s">
         <v>114</v>
-      </c>
-      <c r="I47" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
         <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
         <v>36</v>
@@ -2956,7 +2960,7 @@
         <v>13</v>
       </c>
       <c r="H48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
@@ -2964,13 +2968,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
         <v>36</v>
@@ -2985,7 +2989,7 @@
         <v>13</v>
       </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
@@ -2993,13 +2997,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
         <v>36</v>
@@ -3014,7 +3018,7 @@
         <v>13</v>
       </c>
       <c r="H50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
@@ -3022,13 +3026,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
         <v>36</v>
@@ -3043,7 +3047,7 @@
         <v>13</v>
       </c>
       <c r="H51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
@@ -3051,13 +3055,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D52" t="s">
         <v>36</v>
@@ -3072,7 +3076,7 @@
         <v>13</v>
       </c>
       <c r="H52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
@@ -3080,13 +3084,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
         <v>38</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D53" t="s">
         <v>36</v>
@@ -3101,7 +3105,7 @@
         <v>13</v>
       </c>
       <c r="H53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
@@ -3109,13 +3113,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
         <v>22</v>
@@ -3130,7 +3134,7 @@
         <v>13</v>
       </c>
       <c r="H54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I54" t="s">
         <v>15</v>
@@ -3138,13 +3142,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D55" t="s">
         <v>22</v>
@@ -3159,7 +3163,7 @@
         <v>13</v>
       </c>
       <c r="H55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
@@ -3167,13 +3171,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s">
         <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
         <v>22</v>
@@ -3188,7 +3192,7 @@
         <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
@@ -3196,13 +3200,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
         <v>22</v>
@@ -3217,7 +3221,7 @@
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I57" t="s">
         <v>15</v>
@@ -3225,13 +3229,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s">
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D58" t="s">
         <v>22</v>
@@ -3246,7 +3250,7 @@
         <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I58" t="s">
         <v>15</v>
@@ -3254,13 +3258,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
         <v>22</v>
@@ -3275,7 +3279,7 @@
         <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
@@ -3283,13 +3287,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -3304,7 +3308,7 @@
         <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I60" t="s">
         <v>15</v>
@@ -3312,13 +3316,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s">
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
         <v>36</v>
@@ -3333,7 +3337,7 @@
         <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I61" t="s">
         <v>15</v>
@@ -3341,13 +3345,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D62" t="s">
         <v>22</v>
@@ -3362,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
@@ -3370,13 +3374,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D63" t="s">
         <v>22</v>
@@ -3391,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="H63" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
@@ -3399,13 +3403,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B64" t="s">
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
         <v>22</v>
@@ -3420,7 +3424,7 @@
         <v>13</v>
       </c>
       <c r="H64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I64" t="s">
         <v>15</v>
@@ -3428,13 +3432,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>151</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
         <v>152</v>
-      </c>
-      <c r="B65" t="s">
-        <v>26</v>
-      </c>
-      <c r="C65" t="s">
-        <v>153</v>
       </c>
       <c r="D65" t="s">
         <v>22</v>
@@ -3449,7 +3453,7 @@
         <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I65" t="s">
         <v>15</v>
@@ -3457,13 +3461,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B66" t="s">
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D66" t="s">
         <v>22</v>
@@ -3478,7 +3482,7 @@
         <v>13</v>
       </c>
       <c r="H66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I66" t="s">
         <v>15</v>
@@ -3486,13 +3490,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D67" t="s">
         <v>22</v>
@@ -3507,7 +3511,7 @@
         <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I67" t="s">
         <v>15</v>
@@ -3515,13 +3519,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B68" t="s">
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D68" t="s">
         <v>22</v>
@@ -3536,7 +3540,7 @@
         <v>13</v>
       </c>
       <c r="H68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
@@ -3544,13 +3548,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B69" t="s">
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D69" t="s">
         <v>36</v>
@@ -3565,7 +3569,7 @@
         <v>13</v>
       </c>
       <c r="H69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
@@ -3573,13 +3577,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B70" t="s">
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D70" t="s">
         <v>36</v>
@@ -3594,7 +3598,7 @@
         <v>13</v>
       </c>
       <c r="H70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
@@ -3602,13 +3606,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
         <v>165</v>
-      </c>
-      <c r="B71" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" t="s">
-        <v>166</v>
       </c>
       <c r="D71" t="s">
         <v>22</v>
@@ -3623,7 +3627,7 @@
         <v>13</v>
       </c>
       <c r="H71" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
@@ -3631,13 +3635,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
         <v>165</v>
-      </c>
-      <c r="B72" t="s">
-        <v>26</v>
-      </c>
-      <c r="C72" t="s">
-        <v>166</v>
       </c>
       <c r="D72" t="s">
         <v>43</v>
@@ -3652,7 +3656,7 @@
         <v>13</v>
       </c>
       <c r="H72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
@@ -3660,13 +3664,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B73" t="s">
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D73" t="s">
         <v>22</v>
@@ -3681,7 +3685,7 @@
         <v>13</v>
       </c>
       <c r="H73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
@@ -3689,13 +3693,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B74" t="s">
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D74" t="s">
         <v>22</v>
@@ -3710,21 +3714,21 @@
         <v>13</v>
       </c>
       <c r="H74" t="s">
+        <v>171</v>
+      </c>
+      <c r="I74" t="s">
         <v>172</v>
-      </c>
-      <c r="I74" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
         <v>174</v>
-      </c>
-      <c r="B75" t="s">
-        <v>26</v>
-      </c>
-      <c r="C75" t="s">
-        <v>175</v>
       </c>
       <c r="D75" t="s">
         <v>22</v>
@@ -3739,7 +3743,7 @@
         <v>13</v>
       </c>
       <c r="H75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
@@ -3747,13 +3751,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
         <v>177</v>
-      </c>
-      <c r="B76" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" t="s">
-        <v>178</v>
       </c>
       <c r="D76" t="s">
         <v>22</v>
@@ -3768,7 +3772,7 @@
         <v>13</v>
       </c>
       <c r="H76" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
@@ -3776,13 +3780,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B77" t="s">
         <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D77" t="s">
         <v>36</v>
@@ -3797,7 +3801,7 @@
         <v>13</v>
       </c>
       <c r="H77" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I77" t="s">
         <v>15</v>
@@ -3805,13 +3809,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
         <v>182</v>
-      </c>
-      <c r="B78" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" t="s">
-        <v>183</v>
       </c>
       <c r="D78" t="s">
         <v>22</v>
@@ -3826,7 +3830,7 @@
         <v>13</v>
       </c>
       <c r="H78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I78" t="s">
         <v>15</v>
@@ -3834,13 +3838,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B79" t="s">
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D79" t="s">
         <v>22</v>
@@ -3855,7 +3859,7 @@
         <v>13</v>
       </c>
       <c r="H79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
@@ -3863,13 +3867,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
         <v>26</v>
       </c>
       <c r="C80" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D80" t="s">
         <v>22</v>
@@ -3884,7 +3888,7 @@
         <v>13</v>
       </c>
       <c r="H80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I80" t="s">
         <v>15</v>
@@ -3892,13 +3896,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
         <v>38</v>
       </c>
       <c r="C81" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D81" t="s">
         <v>36</v>
@@ -3913,7 +3917,7 @@
         <v>13</v>
       </c>
       <c r="H81" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
@@ -3921,13 +3925,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>190</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
         <v>191</v>
-      </c>
-      <c r="B82" t="s">
-        <v>26</v>
-      </c>
-      <c r="C82" t="s">
-        <v>192</v>
       </c>
       <c r="D82" t="s">
         <v>22</v>
@@ -3942,7 +3946,7 @@
         <v>13</v>
       </c>
       <c r="H82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
@@ -3950,13 +3954,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B83" t="s">
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D83" t="s">
         <v>22</v>
@@ -3971,7 +3975,7 @@
         <v>13</v>
       </c>
       <c r="H83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
@@ -3979,13 +3983,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D84" t="s">
         <v>36</v>
@@ -4000,7 +4004,7 @@
         <v>13</v>
       </c>
       <c r="H84" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
@@ -4008,13 +4012,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>197</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
         <v>198</v>
-      </c>
-      <c r="B85" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" t="s">
-        <v>199</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -4029,7 +4033,7 @@
         <v>13</v>
       </c>
       <c r="H85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
@@ -4037,13 +4041,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>200</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
         <v>201</v>
-      </c>
-      <c r="B86" t="s">
-        <v>26</v>
-      </c>
-      <c r="C86" t="s">
-        <v>202</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -4058,7 +4062,7 @@
         <v>13</v>
       </c>
       <c r="H86" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I86" t="s">
         <v>15</v>
@@ -4066,13 +4070,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B87" t="s">
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D87" t="s">
         <v>36</v>
@@ -4087,7 +4091,7 @@
         <v>13</v>
       </c>
       <c r="H87" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
@@ -4095,13 +4099,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B88" t="s">
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D88" t="s">
         <v>36</v>
@@ -4116,7 +4120,7 @@
         <v>13</v>
       </c>
       <c r="H88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
@@ -4124,13 +4128,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B89" t="s">
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D89" t="s">
         <v>36</v>
@@ -4145,7 +4149,7 @@
         <v>13</v>
       </c>
       <c r="H89" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I89" t="s">
         <v>15</v>
@@ -4153,13 +4157,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B90" t="s">
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D90" t="s">
         <v>22</v>
@@ -4174,21 +4178,21 @@
         <v>58</v>
       </c>
       <c r="H90" t="s">
+        <v>210</v>
+      </c>
+      <c r="I90" t="s">
         <v>211</v>
-      </c>
-      <c r="I90" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B91" t="s">
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D91" t="s">
         <v>22</v>
@@ -4203,7 +4207,7 @@
         <v>13</v>
       </c>
       <c r="H91" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
@@ -4211,13 +4215,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B92" t="s">
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -4232,7 +4236,7 @@
         <v>13</v>
       </c>
       <c r="H92" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
@@ -4240,13 +4244,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B93" t="s">
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -4261,7 +4265,7 @@
         <v>13</v>
       </c>
       <c r="H93" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I93" t="s">
         <v>15</v>
@@ -4269,13 +4273,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B94" t="s">
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D94" t="s">
         <v>36</v>
@@ -4290,7 +4294,7 @@
         <v>13</v>
       </c>
       <c r="H94" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I94" t="s">
         <v>15</v>
@@ -4298,13 +4302,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>221</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
         <v>222</v>
-      </c>
-      <c r="B95" t="s">
-        <v>26</v>
-      </c>
-      <c r="C95" t="s">
-        <v>223</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -4319,7 +4323,7 @@
         <v>13</v>
       </c>
       <c r="H95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
@@ -4327,13 +4331,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D96" t="s">
         <v>36</v>
@@ -4348,7 +4352,7 @@
         <v>13</v>
       </c>
       <c r="H96" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
@@ -4356,13 +4360,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B97" t="s">
         <v>38</v>
       </c>
       <c r="C97" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D97" t="s">
         <v>36</v>
@@ -4377,7 +4381,7 @@
         <v>13</v>
       </c>
       <c r="H97" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I97" t="s">
         <v>15</v>
@@ -4385,13 +4389,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>227</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
         <v>228</v>
-      </c>
-      <c r="B98" t="s">
-        <v>26</v>
-      </c>
-      <c r="C98" t="s">
-        <v>229</v>
       </c>
       <c r="D98" t="s">
         <v>43</v>
@@ -4406,7 +4410,7 @@
         <v>13</v>
       </c>
       <c r="H98" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
@@ -4414,13 +4418,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B99" t="s">
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D99" t="s">
         <v>43</v>
@@ -4435,7 +4439,7 @@
         <v>13</v>
       </c>
       <c r="H99" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
@@ -4443,13 +4447,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B100" t="s">
         <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D100" t="s">
         <v>43</v>
@@ -4464,7 +4468,7 @@
         <v>13</v>
       </c>
       <c r="H100" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I100" t="s">
         <v>15</v>
@@ -4472,13 +4476,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B101" t="s">
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D101" t="s">
         <v>43</v>
@@ -4493,7 +4497,7 @@
         <v>13</v>
       </c>
       <c r="H101" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I101" t="s">
         <v>15</v>
@@ -4501,13 +4505,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B102" t="s">
         <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D102" t="s">
         <v>43</v>
@@ -4522,7 +4526,7 @@
         <v>13</v>
       </c>
       <c r="H102" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I102" t="s">
         <v>15</v>
@@ -4530,13 +4534,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D103" t="s">
         <v>36</v>
@@ -4551,7 +4555,7 @@
         <v>13</v>
       </c>
       <c r="H103" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
@@ -4559,13 +4563,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B104" t="s">
         <v>38</v>
       </c>
       <c r="C104" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D104" t="s">
         <v>36</v>
@@ -4580,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="H104" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
@@ -4588,13 +4592,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>241</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
         <v>242</v>
-      </c>
-      <c r="B105" t="s">
-        <v>26</v>
-      </c>
-      <c r="C105" t="s">
-        <v>243</v>
       </c>
       <c r="D105" t="s">
         <v>43</v>
@@ -4609,7 +4613,7 @@
         <v>13</v>
       </c>
       <c r="H105" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I105" t="s">
         <v>15</v>
@@ -4617,13 +4621,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B106" t="s">
         <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D106" t="s">
         <v>43</v>
@@ -4638,7 +4642,7 @@
         <v>13</v>
       </c>
       <c r="H106" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
@@ -4646,13 +4650,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B107" t="s">
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D107" t="s">
         <v>22</v>
@@ -4667,7 +4671,7 @@
         <v>13</v>
       </c>
       <c r="H107" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
@@ -4675,13 +4679,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B108" t="s">
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D108" t="s">
         <v>36</v>
@@ -4696,7 +4700,7 @@
         <v>13</v>
       </c>
       <c r="H108" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I108" t="s">
         <v>15</v>
@@ -4704,13 +4708,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B109" t="s">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D109" t="s">
         <v>36</v>
@@ -4725,7 +4729,7 @@
         <v>13</v>
       </c>
       <c r="H109" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I109" t="s">
         <v>15</v>
@@ -4733,13 +4737,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B110" t="s">
         <v>10</v>
       </c>
       <c r="C110" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D110" t="s">
         <v>36</v>
@@ -4754,7 +4758,7 @@
         <v>13</v>
       </c>
       <c r="H110" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I110" t="s">
         <v>15</v>
@@ -4762,13 +4766,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" t="s">
         <v>253</v>
-      </c>
-      <c r="B111" t="s">
-        <v>26</v>
-      </c>
-      <c r="C111" t="s">
-        <v>254</v>
       </c>
       <c r="D111" t="s">
         <v>22</v>
@@ -4783,7 +4787,7 @@
         <v>13</v>
       </c>
       <c r="H111" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
@@ -4791,13 +4795,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B112" t="s">
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D112" t="s">
         <v>22</v>
@@ -4812,7 +4816,7 @@
         <v>13</v>
       </c>
       <c r="H112" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I112" t="s">
         <v>15</v>
@@ -4820,13 +4824,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B113" t="s">
         <v>48</v>
       </c>
       <c r="C113" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
         <v>22</v>
@@ -4841,7 +4845,7 @@
         <v>13</v>
       </c>
       <c r="H113" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I113" t="s">
         <v>15</v>
@@ -4849,13 +4853,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B114" t="s">
         <v>10</v>
       </c>
       <c r="C114" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D114" t="s">
         <v>36</v>
@@ -4870,7 +4874,7 @@
         <v>13</v>
       </c>
       <c r="H114" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I114" t="s">
         <v>15</v>
@@ -4878,13 +4882,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D115" t="s">
         <v>36</v>
@@ -4899,7 +4903,7 @@
         <v>13</v>
       </c>
       <c r="H115" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I115" t="s">
         <v>15</v>
@@ -4907,13 +4911,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>263</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
         <v>264</v>
-      </c>
-      <c r="B116" t="s">
-        <v>26</v>
-      </c>
-      <c r="C116" t="s">
-        <v>265</v>
       </c>
       <c r="D116" t="s">
         <v>22</v>
@@ -4928,7 +4932,7 @@
         <v>13</v>
       </c>
       <c r="H116" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I116" t="s">
         <v>15</v>
@@ -4936,13 +4940,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B117" t="s">
         <v>26</v>
       </c>
       <c r="C117" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D117" t="s">
         <v>22</v>
@@ -4957,7 +4961,7 @@
         <v>13</v>
       </c>
       <c r="H117" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I117" t="s">
         <v>15</v>
@@ -4965,13 +4969,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B118" t="s">
         <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D118" t="s">
         <v>22</v>
@@ -4986,7 +4990,7 @@
         <v>13</v>
       </c>
       <c r="H118" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I118" t="s">
         <v>15</v>
@@ -4994,13 +4998,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B119" t="s">
         <v>26</v>
       </c>
       <c r="C119" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D119" t="s">
         <v>22</v>
@@ -5015,7 +5019,7 @@
         <v>13</v>
       </c>
       <c r="H119" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I119" t="s">
         <v>15</v>
@@ -5023,13 +5027,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B120" t="s">
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D120" t="s">
         <v>36</v>
@@ -5044,7 +5048,7 @@
         <v>13</v>
       </c>
       <c r="H120" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I120" t="s">
         <v>15</v>
@@ -5052,13 +5056,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B121" t="s">
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D121" t="s">
         <v>36</v>
@@ -5073,7 +5077,7 @@
         <v>13</v>
       </c>
       <c r="H121" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I121" t="s">
         <v>15</v>
@@ -5081,13 +5085,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B122" t="s">
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D122" t="s">
         <v>36</v>
@@ -5102,7 +5106,7 @@
         <v>13</v>
       </c>
       <c r="H122" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I122" t="s">
         <v>15</v>
@@ -5110,13 +5114,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B123" t="s">
         <v>10</v>
       </c>
       <c r="C123" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D123" t="s">
         <v>36</v>
@@ -5131,7 +5135,7 @@
         <v>13</v>
       </c>
       <c r="H123" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I123" t="s">
         <v>15</v>
@@ -5139,13 +5143,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>279</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
         <v>280</v>
-      </c>
-      <c r="B124" t="s">
-        <v>26</v>
-      </c>
-      <c r="C124" t="s">
-        <v>281</v>
       </c>
       <c r="D124" t="s">
         <v>22</v>
@@ -5160,7 +5164,7 @@
         <v>13</v>
       </c>
       <c r="H124" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I124" t="s">
         <v>15</v>
@@ -5168,13 +5172,13 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B125" t="s">
         <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D125" t="s">
         <v>36</v>
@@ -5189,7 +5193,7 @@
         <v>13</v>
       </c>
       <c r="H125" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I125" t="s">
         <v>15</v>
@@ -5203,7 +5207,7 @@
         <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D126" t="s">
         <v>12</v>
@@ -5218,10 +5222,10 @@
         <v>58</v>
       </c>
       <c r="H126" t="s">
+        <v>285</v>
+      </c>
+      <c r="I126" t="s">
         <v>286</v>
-      </c>
-      <c r="I126" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -5232,7 +5236,7 @@
         <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D127" t="s">
         <v>36</v>
@@ -5247,7 +5251,7 @@
         <v>13</v>
       </c>
       <c r="H127" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I127" t="s">
         <v>15</v>
@@ -5261,7 +5265,7 @@
         <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D128" t="s">
         <v>36</v>
@@ -5276,7 +5280,7 @@
         <v>13</v>
       </c>
       <c r="H128" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I128" t="s">
         <v>15</v>
@@ -5284,13 +5288,13 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B129" t="s">
         <v>38</v>
       </c>
       <c r="C129" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D129" t="s">
         <v>36</v>
@@ -5305,7 +5309,7 @@
         <v>13</v>
       </c>
       <c r="H129" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I129" t="s">
         <v>15</v>
@@ -5313,13 +5317,13 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B130" t="s">
         <v>38</v>
       </c>
       <c r="C130" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D130" t="s">
         <v>36</v>
@@ -5334,7 +5338,7 @@
         <v>13</v>
       </c>
       <c r="H130" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I130" t="s">
         <v>15</v>
@@ -5342,13 +5346,13 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B131" t="s">
         <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D131" t="s">
         <v>36</v>
@@ -5363,7 +5367,7 @@
         <v>13</v>
       </c>
       <c r="H131" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I131" t="s">
         <v>15</v>
@@ -5371,13 +5375,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B132" t="s">
         <v>10</v>
       </c>
       <c r="C132" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D132" t="s">
         <v>22</v>
@@ -5392,21 +5396,21 @@
         <v>13</v>
       </c>
       <c r="H132" t="s">
+        <v>296</v>
+      </c>
+      <c r="I132" t="s">
         <v>297</v>
-      </c>
-      <c r="I132" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B133" t="s">
         <v>38</v>
       </c>
       <c r="C133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D133" t="s">
         <v>36</v>
@@ -5421,7 +5425,7 @@
         <v>13</v>
       </c>
       <c r="H133" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I133" t="s">
         <v>15</v>
@@ -5429,13 +5433,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B134" t="s">
         <v>26</v>
       </c>
       <c r="C134" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D134" t="s">
         <v>22</v>
@@ -5450,7 +5454,7 @@
         <v>13</v>
       </c>
       <c r="H134" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I134" t="s">
         <v>15</v>
@@ -5458,13 +5462,13 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B135" t="s">
         <v>38</v>
       </c>
       <c r="C135" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D135" t="s">
         <v>36</v>
@@ -5479,7 +5483,7 @@
         <v>13</v>
       </c>
       <c r="H135" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I135" t="s">
         <v>15</v>
@@ -5487,13 +5491,13 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B136" t="s">
         <v>48</v>
       </c>
       <c r="C136" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D136" t="s">
         <v>36</v>
@@ -5508,7 +5512,7 @@
         <v>13</v>
       </c>
       <c r="H136" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I136" t="s">
         <v>15</v>
@@ -5516,13 +5520,13 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B137" t="s">
         <v>10</v>
       </c>
       <c r="C137" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D137" t="s">
         <v>22</v>
@@ -5537,7 +5541,7 @@
         <v>13</v>
       </c>
       <c r="H137" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I137" t="s">
         <v>15</v>
@@ -5545,13 +5549,13 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B138" t="s">
         <v>38</v>
       </c>
       <c r="C138" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D138" t="s">
         <v>36</v>
@@ -5566,7 +5570,7 @@
         <v>13</v>
       </c>
       <c r="H138" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I138" t="s">
         <v>15</v>
@@ -5574,13 +5578,13 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B139" t="s">
         <v>38</v>
       </c>
       <c r="C139" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D139" t="s">
         <v>36</v>
@@ -5595,7 +5599,7 @@
         <v>13</v>
       </c>
       <c r="H139" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I139" t="s">
         <v>15</v>
@@ -5603,13 +5607,13 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B140" t="s">
         <v>10</v>
       </c>
       <c r="C140" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D140" t="s">
         <v>22</v>
@@ -5624,21 +5628,21 @@
         <v>13</v>
       </c>
       <c r="H140" t="s">
+        <v>310</v>
+      </c>
+      <c r="I140" t="s">
         <v>311</v>
-      </c>
-      <c r="I140" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B141" t="s">
         <v>26</v>
       </c>
       <c r="C141" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D141" t="s">
         <v>22</v>
@@ -5653,7 +5657,7 @@
         <v>13</v>
       </c>
       <c r="H141" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I141" t="s">
         <v>15</v>
@@ -5661,13 +5665,13 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B142" t="s">
         <v>38</v>
       </c>
       <c r="C142" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D142" t="s">
         <v>22</v>
@@ -5682,21 +5686,21 @@
         <v>58</v>
       </c>
       <c r="H142" t="s">
+        <v>314</v>
+      </c>
+      <c r="I142" t="s">
         <v>315</v>
-      </c>
-      <c r="I142" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B143" t="s">
         <v>48</v>
       </c>
       <c r="C143" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D143" t="s">
         <v>36</v>
@@ -5711,7 +5715,7 @@
         <v>13</v>
       </c>
       <c r="H143" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I143" t="s">
         <v>15</v>
@@ -5719,13 +5723,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B144" t="s">
         <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D144" t="s">
         <v>36</v>
@@ -5740,21 +5744,21 @@
         <v>58</v>
       </c>
       <c r="H144" t="s">
+        <v>318</v>
+      </c>
+      <c r="I144" t="s">
         <v>319</v>
-      </c>
-      <c r="I144" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B145" t="s">
         <v>10</v>
       </c>
       <c r="C145" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D145" t="s">
         <v>36</v>
@@ -5769,7 +5773,7 @@
         <v>13</v>
       </c>
       <c r="H145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I145" t="s">
         <v>15</v>
@@ -5777,13 +5781,13 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B146" t="s">
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D146" t="s">
         <v>22</v>
@@ -5798,7 +5802,7 @@
         <v>13</v>
       </c>
       <c r="H146" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I146" t="s">
         <v>15</v>
@@ -5806,13 +5810,13 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B147" t="s">
         <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D147" t="s">
         <v>43</v>
@@ -5827,7 +5831,7 @@
         <v>13</v>
       </c>
       <c r="H147" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I147" t="s">
         <v>15</v>
@@ -5835,13 +5839,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B148" t="s">
         <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D148" t="s">
         <v>22</v>
@@ -5856,21 +5860,21 @@
         <v>13</v>
       </c>
       <c r="H148" t="s">
+        <v>325</v>
+      </c>
+      <c r="I148" t="s">
         <v>326</v>
-      </c>
-      <c r="I148" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>127</v>
+      </c>
+      <c r="B149" t="s">
+        <v>327</v>
+      </c>
+      <c r="C149" t="s">
         <v>128</v>
-      </c>
-      <c r="B149" t="s">
-        <v>328</v>
-      </c>
-      <c r="C149" t="s">
-        <v>129</v>
       </c>
       <c r="D149" t="s">
         <v>22</v>
@@ -5885,7 +5889,7 @@
         <v>13</v>
       </c>
       <c r="H149" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I149" t="s">
         <v>15</v>
@@ -5893,13 +5897,13 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>144</v>
+      </c>
+      <c r="B150" t="s">
+        <v>327</v>
+      </c>
+      <c r="C150" t="s">
         <v>145</v>
-      </c>
-      <c r="B150" t="s">
-        <v>328</v>
-      </c>
-      <c r="C150" t="s">
-        <v>146</v>
       </c>
       <c r="D150" t="s">
         <v>22</v>
@@ -5914,7 +5918,7 @@
         <v>13</v>
       </c>
       <c r="H150" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I150" t="s">
         <v>15</v>
@@ -5922,13 +5926,13 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D151" t="s">
         <v>43</v>
@@ -5943,7 +5947,7 @@
         <v>13</v>
       </c>
       <c r="H151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I151" t="s">
         <v>15</v>
@@ -5951,13 +5955,13 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B152" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C152" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D152" t="s">
         <v>22</v>
@@ -5972,10 +5976,10 @@
         <v>13</v>
       </c>
       <c r="H152" t="s">
+        <v>333</v>
+      </c>
+      <c r="I152" t="s">
         <v>334</v>
-      </c>
-      <c r="I152" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -5986,7 +5990,7 @@
         <v>10</v>
       </c>
       <c r="C153" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D153" t="s">
         <v>12</v>
@@ -6004,18 +6008,18 @@
         <v>23</v>
       </c>
       <c r="I153" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B154" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C154" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D154" t="s">
         <v>36</v>
@@ -6030,7 +6034,7 @@
         <v>13</v>
       </c>
       <c r="H154" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I154" t="s">
         <v>15</v>
@@ -6038,13 +6042,13 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B155" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C155" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D155" t="s">
         <v>36</v>
@@ -6059,7 +6063,7 @@
         <v>13</v>
       </c>
       <c r="H155" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I155" t="s">
         <v>15</v>
@@ -6067,13 +6071,13 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B156" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C156" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D156" t="s">
         <v>36</v>
@@ -6088,7 +6092,7 @@
         <v>13</v>
       </c>
       <c r="H156" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I156" t="s">
         <v>15</v>
@@ -6096,13 +6100,13 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B157" t="s">
         <v>26</v>
       </c>
       <c r="C157" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D157" t="s">
         <v>22</v>
@@ -6117,7 +6121,7 @@
         <v>13</v>
       </c>
       <c r="H157" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I157" t="s">
         <v>15</v>
@@ -6125,13 +6129,13 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B158" t="s">
         <v>38</v>
       </c>
       <c r="C158" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D158" t="s">
         <v>22</v>
@@ -6146,7 +6150,7 @@
         <v>13</v>
       </c>
       <c r="H158" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I158" t="s">
         <v>15</v>
@@ -6154,13 +6158,13 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B159" t="s">
         <v>48</v>
       </c>
       <c r="C159" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D159" t="s">
         <v>36</v>
@@ -6175,7 +6179,7 @@
         <v>13</v>
       </c>
       <c r="H159" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I159" t="s">
         <v>15</v>
@@ -6183,13 +6187,13 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D160" t="s">
         <v>22</v>
@@ -6204,7 +6208,7 @@
         <v>13</v>
       </c>
       <c r="H160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I160" t="s">
         <v>15</v>
@@ -6212,13 +6216,13 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B161" t="s">
         <v>38</v>
       </c>
       <c r="C161" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D161" t="s">
         <v>36</v>
@@ -6233,7 +6237,7 @@
         <v>13</v>
       </c>
       <c r="H161" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I161" t="s">
         <v>15</v>
@@ -6241,13 +6245,13 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B162" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C162" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D162" t="s">
         <v>36</v>
@@ -6262,7 +6266,7 @@
         <v>13</v>
       </c>
       <c r="H162" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I162" t="s">
         <v>15</v>
@@ -6270,13 +6274,13 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B163" t="s">
         <v>10</v>
       </c>
       <c r="C163" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D163" t="s">
         <v>43</v>
@@ -6291,21 +6295,21 @@
         <v>58</v>
       </c>
       <c r="H163" t="s">
+        <v>348</v>
+      </c>
+      <c r="I163" t="s">
         <v>349</v>
-      </c>
-      <c r="I163" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B164" t="s">
         <v>10</v>
       </c>
       <c r="C164" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D164" t="s">
         <v>12</v>
@@ -6320,22 +6324,22 @@
         <v>13</v>
       </c>
       <c r="H164" t="s">
+        <v>351</v>
+      </c>
+      <c r="I164" t="s">
         <v>352</v>
-      </c>
-      <c r="I164" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6358,10 +6362,10 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" t="s">
         <v>354</v>
-      </c>
-      <c r="F1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6378,10 +6382,10 @@
         <v>820</v>
       </c>
       <c r="E2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F2" t="s">
         <v>356</v>
-      </c>
-      <c r="F2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6398,10 +6402,10 @@
         <v>201</v>
       </c>
       <c r="E3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F3" t="s">
         <v>358</v>
-      </c>
-      <c r="F3" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6418,10 +6422,10 @@
         <v>201</v>
       </c>
       <c r="E4" t="s">
+        <v>359</v>
+      </c>
+      <c r="F4" t="s">
         <v>360</v>
-      </c>
-      <c r="F4" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6438,10 +6442,10 @@
         <v>240</v>
       </c>
       <c r="E5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F5" t="s">
         <v>362</v>
-      </c>
-      <c r="F5" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6458,10 +6462,10 @@
         <v>461</v>
       </c>
       <c r="E6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F6" t="s">
         <v>360</v>
-      </c>
-      <c r="F6" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6478,10 +6482,10 @@
         <v>308</v>
       </c>
       <c r="E7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F7" t="s">
         <v>364</v>
-      </c>
-      <c r="F7" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6498,10 +6502,10 @@
         <v>271</v>
       </c>
       <c r="E8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F8" t="s">
         <v>364</v>
-      </c>
-      <c r="F8" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6512,16 +6516,16 @@
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9">
         <v>479</v>
       </c>
       <c r="E9" t="s">
+        <v>365</v>
+      </c>
+      <c r="F9" t="s">
         <v>366</v>
-      </c>
-      <c r="F9" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6532,16 +6536,16 @@
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10">
         <v>455</v>
       </c>
       <c r="E10" t="s">
+        <v>367</v>
+      </c>
+      <c r="F10" t="s">
         <v>368</v>
-      </c>
-      <c r="F10" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6552,16 +6556,16 @@
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11">
         <v>255</v>
       </c>
       <c r="E11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F11" t="s">
         <v>370</v>
-      </c>
-      <c r="F11" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6572,316 +6576,316 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12">
         <v>628</v>
       </c>
       <c r="E12" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12" t="s">
         <v>364</v>
-      </c>
-      <c r="F12" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>455</v>
       </c>
       <c r="E13" t="s">
+        <v>371</v>
+      </c>
+      <c r="F13" t="s">
         <v>372</v>
-      </c>
-      <c r="F13" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14">
         <v>219</v>
       </c>
       <c r="E14" t="s">
+        <v>359</v>
+      </c>
+      <c r="F14" t="s">
         <v>360</v>
-      </c>
-      <c r="F14" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15">
         <v>331</v>
       </c>
       <c r="E15" t="s">
+        <v>373</v>
+      </c>
+      <c r="F15" t="s">
         <v>374</v>
-      </c>
-      <c r="F15" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D16">
         <v>368</v>
       </c>
       <c r="E16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F16" t="s">
         <v>376</v>
-      </c>
-      <c r="F16" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D17">
         <v>824</v>
       </c>
       <c r="E17" t="s">
+        <v>377</v>
+      </c>
+      <c r="F17" t="s">
         <v>378</v>
-      </c>
-      <c r="F17" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D18">
         <v>410</v>
       </c>
       <c r="E18" t="s">
+        <v>379</v>
+      </c>
+      <c r="F18" t="s">
         <v>380</v>
-      </c>
-      <c r="F18" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D19">
         <v>250</v>
       </c>
       <c r="E19" t="s">
+        <v>381</v>
+      </c>
+      <c r="F19" t="s">
         <v>382</v>
-      </c>
-      <c r="F19" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D20">
         <v>211</v>
       </c>
       <c r="E20" t="s">
+        <v>363</v>
+      </c>
+      <c r="F20" t="s">
         <v>364</v>
-      </c>
-      <c r="F20" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D21">
         <v>290</v>
       </c>
       <c r="E21" t="s">
+        <v>359</v>
+      </c>
+      <c r="F21" t="s">
         <v>360</v>
-      </c>
-      <c r="F21" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D22">
         <v>218</v>
       </c>
       <c r="E22" t="s">
+        <v>381</v>
+      </c>
+      <c r="F22" t="s">
         <v>382</v>
-      </c>
-      <c r="F22" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D23">
         <v>409</v>
       </c>
       <c r="E23" t="s">
+        <v>381</v>
+      </c>
+      <c r="F23" t="s">
         <v>382</v>
-      </c>
-      <c r="F23" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D24">
         <v>211</v>
       </c>
       <c r="E24" t="s">
+        <v>381</v>
+      </c>
+      <c r="F24" t="s">
         <v>382</v>
-      </c>
-      <c r="F24" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D25">
         <v>204</v>
       </c>
       <c r="E25" t="s">
+        <v>381</v>
+      </c>
+      <c r="F25" t="s">
         <v>382</v>
-      </c>
-      <c r="F25" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D26">
         <v>465</v>
       </c>
       <c r="E26" t="s">
+        <v>381</v>
+      </c>
+      <c r="F26" t="s">
         <v>382</v>
-      </c>
-      <c r="F26" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D27">
         <v>378</v>
       </c>
       <c r="E27" t="s">
+        <v>381</v>
+      </c>
+      <c r="F27" t="s">
         <v>382</v>
-      </c>
-      <c r="F27" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -6892,50 +6896,50 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D28">
         <v>282</v>
       </c>
       <c r="E28" t="s">
+        <v>383</v>
+      </c>
+      <c r="F28" t="s">
         <v>384</v>
-      </c>
-      <c r="F28" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D29">
         <v>687</v>
       </c>
       <c r="E29" t="s">
+        <v>373</v>
+      </c>
+      <c r="F29" t="s">
         <v>374</v>
-      </c>
-      <c r="F29" t="s">
-        <v>375</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>